--- a/Matrice_Trasabilitate.xlsx
+++ b/Matrice_Trasabilitate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D&amp;A\Documents\APSII_Curierat\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danni\Desktop\Curierat_Optimizare-main\Curierat_Optimizare-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82CCDC2-7328-489B-B66B-F70793BCA76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A5C318-381C-4781-9081-959E46D6C520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matrice Trasabilitate Cerințe S" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
   <si>
     <t>Cazul de utilizare / Cerinta</t>
   </si>
@@ -197,6 +197,18 @@
   </si>
   <si>
     <t>Test de integrare, Test automat de flux</t>
+  </si>
+  <si>
+    <t>Reprogramare livrare colet</t>
+  </si>
+  <si>
+    <t>REQ-9.1 Sistemul trebuie sa permita Clientului să modifice data de livrare.</t>
+  </si>
+  <si>
+    <t>Ecran reprogramare livrare (Calendar și selector interval orar)</t>
+  </si>
+  <si>
+    <t>Java, SQL, XML</t>
   </si>
 </sst>
 </file>
@@ -238,12 +250,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -462,7 +480,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="146" customWidth="1"/>
@@ -693,6 +711,25 @@
         <v>58</v>
       </c>
     </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
